--- a/data/AttributeAllocRatio.xlsx
+++ b/data/AttributeAllocRatio.xlsx
@@ -536,8 +536,8 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.25</v>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>力量→物伤:非对应职业 +25%</t>
+          <t>力量满投：物伤提高100%</t>
         </is>
       </c>
     </row>
@@ -570,8 +570,8 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.3</v>
+      <c r="F7">
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>力量→物伤:破军 +30%</t>
+          <t>破军力量满投：物伤提高125%</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.15</v>
+      <c r="E8">
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.225</v>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>灵力→法伤 +22.5% / 法力 +15%:非对应职业</t>
+          <t>灵力满投：法伤提高100%，法力提高50%</t>
         </is>
       </c>
     </row>
@@ -635,14 +635,14 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.15</v>
+      <c r="E9">
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.27</v>
+      <c r="G9">
+        <v>1.25</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>灵力→法伤 +27% / 法力 +15%:玄霄</t>
+          <t>玄霄灵力满投：法伤提高125%，法力提高50%</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.1667</v>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>敏捷→速度:非对应职业 +16.67%</t>
+          <t>敏捷满投：速度提高100%</t>
         </is>
       </c>
     </row>
@@ -712,15 +712,15 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.2</v>
+      <c r="H11">
+        <v>1.25</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>敏捷→速度:逐风 +20%</t>
+          <t>逐风敏捷满投：速度提高125%</t>
         </is>
       </c>
     </row>
@@ -734,8 +734,8 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.2083</v>
+      <c r="D12">
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -749,12 +749,12 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.1</v>
+      <c r="I12">
+        <v>0.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>体质→气血 +20.83% / 防御 +10%:非对应职业</t>
+          <t>体质满投：气血提高200%，防御提高80%</t>
         </is>
       </c>
     </row>
@@ -768,8 +768,8 @@
       <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.25</v>
+      <c r="D13">
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -783,12 +783,12 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.12</v>
+      <c r="I13">
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>体质→气血 +25% / 防御 +12%:丹心</t>
+          <t>丹心体质满投：气血提高250%，防御提高100%</t>
         </is>
       </c>
     </row>
